--- a/rtos-api-analysis/results/states/ThreadX_states_analysis.xlsx
+++ b/rtos-api-analysis/results/states/ThreadX_states_analysis.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,10 +501,10 @@
         <v>26.2626</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="3">
@@ -532,10 +532,10 @@
         <v>93.5018</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.72</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="6">
@@ -625,10 +625,10 @@
         <v>0.809213</v>
       </c>
       <c r="H6" t="n">
-        <v>1.73</v>
+        <v>5.18</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="7">
@@ -687,10 +687,10 @@
         <v>27.4809</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -749,10 +749,10 @@
         <v>26.4151</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="11">
@@ -780,10 +780,10 @@
         <v>37.6812</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -820,107 +820,107 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>byte_release</t>
+          <t>semaphore_performance_info_get</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2545</v>
+        <v>140</v>
       </c>
       <c r="C13" t="n">
-        <v>7509</v>
+        <v>169</v>
       </c>
       <c r="D13" t="n">
-        <v>2896</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>38.5671</v>
+        <v>0.591716</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="G13" t="n">
-        <v>0.106539</v>
+        <v>86.3905</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>byte_pool_create</t>
+          <t>thread_stack_error_notify</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>9.863950000000001</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>42.1769</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>semaphore_performance_info_get</t>
+          <t>mutex_info_get</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>140</v>
+        <v>932</v>
       </c>
       <c r="C15" t="n">
-        <v>169</v>
+        <v>963</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.591716</v>
+        <v>1.34995</v>
       </c>
       <c r="F15" t="n">
-        <v>146</v>
+        <v>926</v>
       </c>
       <c r="G15" t="n">
-        <v>86.3905</v>
+        <v>96.15779999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>thread_stack_error_notify</t>
+          <t>thread_relinquish</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -944,38 +944,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mutex_info_get</t>
+          <t>semaphore_prioritize</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>932</v>
+        <v>92</v>
       </c>
       <c r="C17" t="n">
-        <v>963</v>
+        <v>166</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>1.34995</v>
+        <v>43.9759</v>
       </c>
       <c r="F17" t="n">
-        <v>926</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>96.15779999999999</v>
+        <v>15.6627</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.28</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>thread_relinquish</t>
+          <t>time_get</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1006,324 +1006,324 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>semaphore_prioritize</t>
+          <t>semaphore_performance_system_info_get</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>43.9759</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>15.6627</v>
+        <v>70.5882</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time_get</t>
+          <t>thread_delete</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>22.807</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>28.0702</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>semaphore_performance_system_info_get</t>
+          <t>thread_reset</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>36.2963</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>70.5882</v>
+        <v>19.2593</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>thread_delete</t>
+          <t>block_allocate</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C22" t="n">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E22" t="n">
-        <v>22.807</v>
+        <v>18.7817</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="G22" t="n">
-        <v>28.0702</v>
+        <v>37.5635</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>thread_reset</t>
+          <t>trace_enable</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>36.2963</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>19.2593</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>block_allocate</t>
+          <t>mutex_performance_info_get</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="C24" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>18.7817</v>
+        <v>0.4329</v>
       </c>
       <c r="F24" t="n">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="G24" t="n">
-        <v>37.5635</v>
+        <v>89.17749999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>trace_enable</t>
+          <t>thread_create</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>737</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3020</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>19.9007</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>20.4636</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mutex_performance_info_get</t>
+          <t>byte_pool_performance_system_info_get</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200</v>
+        <v>22</v>
       </c>
       <c r="C26" t="n">
-        <v>231</v>
+        <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4329</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>89.17749999999999</v>
+        <v>72.41379999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.28</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>timer_create</t>
+          <t>event_flags_performance_info_get</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>285</v>
+        <v>140</v>
       </c>
       <c r="C27" t="n">
-        <v>1435</v>
+        <v>169</v>
       </c>
       <c r="D27" t="n">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>10.9408</v>
+        <v>0.591716</v>
       </c>
       <c r="F27" t="n">
-        <v>282</v>
+        <v>146</v>
       </c>
       <c r="G27" t="n">
-        <v>19.6516</v>
+        <v>86.3905</v>
       </c>
       <c r="H27" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.39</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>thread_create</t>
+          <t>timer_change</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>737</v>
+        <v>44</v>
       </c>
       <c r="C28" t="n">
-        <v>3020</v>
+        <v>83</v>
       </c>
       <c r="D28" t="n">
-        <v>601</v>
+        <v>25</v>
       </c>
       <c r="E28" t="n">
-        <v>19.9007</v>
+        <v>30.1205</v>
       </c>
       <c r="F28" t="n">
-        <v>618</v>
+        <v>38</v>
       </c>
       <c r="G28" t="n">
-        <v>20.4636</v>
+        <v>45.7831</v>
       </c>
       <c r="H28" t="n">
-        <v>0.83</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.85</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>byte_pool_performance_system_info_get</t>
+          <t>module_callback_request_thread_entry</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1332,84 +1332,84 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>72.41379999999999</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>event_flags_performance_info_get</t>
+          <t>semaphore_get</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="C30" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
-        <v>0.591716</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>86.3905</v>
+        <v>25.6757</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>timer_change</t>
+          <t>thread_time_slice_change</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D31" t="n">
         <v>25</v>
       </c>
       <c r="E31" t="n">
-        <v>30.1205</v>
+        <v>23.3645</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="G31" t="n">
-        <v>45.7831</v>
+        <v>57.9439</v>
       </c>
       <c r="H31" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>module_callback_request_thread_entry</t>
+          <t>time_set</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1440,26 +1440,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>module_thread_system_suspend</t>
+          <t>trace_event_unfilter</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>33.3333</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1471,782 +1471,782 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>semaphore_get</t>
+          <t>thread_entry_exit_notify</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C34" t="n">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="D34" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>35.3448</v>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G34" t="n">
-        <v>25.6757</v>
+        <v>24.1379</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>thread_time_slice_change</t>
+          <t>queue_performance_info_get</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="C35" t="n">
-        <v>107</v>
+        <v>231</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>23.3645</v>
+        <v>0.4329</v>
       </c>
       <c r="F35" t="n">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="G35" t="n">
-        <v>57.9439</v>
+        <v>89.17749999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>thread_wait_abort</t>
+          <t>trace_event_filter</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>776</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>2517</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1081</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>42.948</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1.03298</v>
+        <v>33.3333</v>
       </c>
       <c r="H36" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>time_set</t>
+          <t>queue_prioritize</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>43.9759</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>15.6627</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>trace_event_unfilter</t>
+          <t>queue_delete</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>19.3798</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
-        <v>33.3333</v>
+        <v>20.155</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>thread_entry_exit_notify</t>
+          <t>thread_sleep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>35.3448</v>
+        <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>24.1379</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>queue_performance_info_get</t>
+          <t>timer_performance_info_get</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>170</v>
+      </c>
+      <c r="C40" t="n">
         <v>200</v>
-      </c>
-      <c r="C40" t="n">
-        <v>231</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4329</v>
+        <v>0.5</v>
       </c>
       <c r="F40" t="n">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="G40" t="n">
-        <v>89.17749999999999</v>
+        <v>88</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>trace_event_filter</t>
+          <t>byte_allocate</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>490</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>11.4286</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="G41" t="n">
-        <v>33.3333</v>
+        <v>22.449</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>queue_prioritize</t>
+          <t>mutex_delete</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="C42" t="n">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="D42" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="E42" t="n">
-        <v>43.9759</v>
+        <v>25.2525</v>
       </c>
       <c r="F42" t="n">
         <v>26</v>
       </c>
       <c r="G42" t="n">
-        <v>15.6627</v>
+        <v>26.2626</v>
       </c>
       <c r="H42" t="n">
         <v>0.1</v>
       </c>
       <c r="I42" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>queue_delete</t>
+          <t>mutex_prioritize</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="C43" t="n">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="E43" t="n">
-        <v>19.3798</v>
+        <v>43.9759</v>
       </c>
       <c r="F43" t="n">
         <v>26</v>
       </c>
       <c r="G43" t="n">
-        <v>20.155</v>
+        <v>15.6627</v>
       </c>
       <c r="H43" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="I43" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>thread_sleep</t>
+          <t>block_pool_prioritize</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>166</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>43.9759</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>15.6627</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>timer_performance_info_get</t>
+          <t>block_pool_delete</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="C45" t="n">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5</v>
+        <v>25.2525</v>
       </c>
       <c r="F45" t="n">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="G45" t="n">
-        <v>88</v>
+        <v>26.2626</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I45" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>byte_allocate</t>
+          <t>event_flags_create</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="C46" t="n">
-        <v>476</v>
+        <v>227</v>
       </c>
       <c r="D46" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E46" t="n">
-        <v>10.9244</v>
+        <v>12.7753</v>
       </c>
       <c r="F46" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="G46" t="n">
-        <v>23.1092</v>
+        <v>31.7181</v>
       </c>
       <c r="H46" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="I46" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mutex_delete</t>
+          <t>block_pool_performance_system_info_get</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C47" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>25.2525</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>26.2626</v>
+        <v>70.5882</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>mutex_prioritize</t>
+          <t>module_object_deallocate</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>166</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>43.9759</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>15.6627</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>block_pool_prioritize</t>
+          <t>queue_performance_system_info_get</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C49" t="n">
-        <v>166</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>43.9759</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6627</v>
+        <v>72</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>block_pool_delete</t>
+          <t>semaphore_ceiling_put</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>1148</v>
       </c>
       <c r="C50" t="n">
-        <v>99</v>
+        <v>3238</v>
       </c>
       <c r="D50" t="n">
-        <v>25</v>
+        <v>1249</v>
       </c>
       <c r="E50" t="n">
-        <v>25.2525</v>
+        <v>38.5732</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="G50" t="n">
-        <v>26.2626</v>
+        <v>1.54416</v>
       </c>
       <c r="H50" t="n">
-        <v>0.03</v>
+        <v>5.18</v>
       </c>
       <c r="I50" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>event_flags_create</t>
+          <t>byte_pool_delete</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C51" t="n">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="D51" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E51" t="n">
-        <v>12.7753</v>
+        <v>25.2525</v>
       </c>
       <c r="F51" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="G51" t="n">
-        <v>31.7181</v>
+        <v>26.2626</v>
       </c>
       <c r="H51" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>block_pool_performance_system_info_get</t>
+          <t>byte_pool_info_get</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>932</v>
+      </c>
+      <c r="C52" t="n">
+        <v>963</v>
+      </c>
+      <c r="D52" t="n">
         <v>13</v>
       </c>
-      <c r="C52" t="n">
-        <v>17</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1.34995</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>926</v>
       </c>
       <c r="G52" t="n">
-        <v>70.5882</v>
+        <v>96.15779999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.02</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>module_object_deallocate</t>
+          <t>thread_resume</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1305</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>49.7318</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1.99234</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>queue_performance_system_info_get</t>
+          <t>mutex_create</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>405</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>13.5802</v>
       </c>
       <c r="F54" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="G54" t="n">
-        <v>72</v>
+        <v>24.1975</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I54" t="n">
-        <v>0.02</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>queue_receive</t>
+          <t>byte_pool_prioritize</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4460</v>
+        <v>92</v>
       </c>
       <c r="C55" t="n">
-        <v>12893</v>
+        <v>166</v>
       </c>
       <c r="D55" t="n">
-        <v>5053</v>
+        <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>39.1918</v>
+        <v>43.9759</v>
       </c>
       <c r="F55" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="G55" t="n">
-        <v>0.573955</v>
+        <v>15.6627</v>
       </c>
       <c r="H55" t="n">
-        <v>6.99</v>
+        <v>0.3</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>semaphore_ceiling_put</t>
+          <t>byte_pool_performance_info_get</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1148</v>
+        <v>230</v>
       </c>
       <c r="C56" t="n">
-        <v>3238</v>
+        <v>262</v>
       </c>
       <c r="D56" t="n">
-        <v>1249</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>38.5732</v>
+        <v>0.381679</v>
       </c>
       <c r="F56" t="n">
-        <v>50</v>
+        <v>236</v>
       </c>
       <c r="G56" t="n">
-        <v>1.54416</v>
+        <v>90.0763</v>
       </c>
       <c r="H56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>timer_performance_system_info_get</t>
+          <t>block_pool_info_get</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>16</v>
+        <v>932</v>
       </c>
       <c r="C57" t="n">
-        <v>21</v>
+        <v>963</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1.34995</v>
       </c>
       <c r="F57" t="n">
-        <v>15</v>
+        <v>926</v>
       </c>
       <c r="G57" t="n">
-        <v>71.4286</v>
+        <v>96.15779999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I57" t="n">
-        <v>0.02</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>byte_pool_delete</t>
+          <t>thread_suspend</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="C58" t="n">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="D58" t="n">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="E58" t="n">
-        <v>25.2525</v>
+        <v>35.2751</v>
       </c>
       <c r="F58" t="n">
         <v>26</v>
       </c>
       <c r="G58" t="n">
-        <v>26.2626</v>
+        <v>8.414239999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.03</v>
+        <v>0.45</v>
       </c>
       <c r="I58" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>byte_pool_info_get</t>
+          <t>queue_info_get</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2268,426 +2268,426 @@
         <v>96.15779999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I59" t="n">
-        <v>1.28</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>thread_resume</t>
+          <t>event_flags_set_notify</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>404</v>
+        <v>40</v>
       </c>
       <c r="C60" t="n">
-        <v>1305</v>
+        <v>106</v>
       </c>
       <c r="D60" t="n">
-        <v>649</v>
+        <v>31</v>
       </c>
       <c r="E60" t="n">
-        <v>49.7318</v>
+        <v>29.2453</v>
       </c>
       <c r="F60" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G60" t="n">
-        <v>1.99234</v>
+        <v>26.4151</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9</v>
+        <v>0.13</v>
       </c>
       <c r="I60" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>mutex_create</t>
+          <t>trace_disable</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>405</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>13.5802</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>24.1975</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>byte_pool_prioritize</t>
+          <t>thread_preemption_change</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C62" t="n">
-        <v>166</v>
+        <v>107</v>
       </c>
       <c r="D62" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="E62" t="n">
-        <v>43.9759</v>
+        <v>23.3645</v>
       </c>
       <c r="F62" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="G62" t="n">
-        <v>15.6627</v>
+        <v>57.9439</v>
       </c>
       <c r="H62" t="n">
         <v>0.1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>semaphore_info_get</t>
+          <t>trace_interrupt_control</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>524</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>554</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>2.34657</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>93.5018</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>byte_pool_performance_info_get</t>
+          <t>thread_priority_change</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="C64" t="n">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E64" t="n">
-        <v>0.381679</v>
+        <v>21.0084</v>
       </c>
       <c r="F64" t="n">
-        <v>236</v>
+        <v>74</v>
       </c>
       <c r="G64" t="n">
-        <v>90.0763</v>
+        <v>62.1849</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>semaphore_put_notify</t>
+          <t>timer_activate</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C65" t="n">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="D65" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="E65" t="n">
-        <v>29.2453</v>
+        <v>68.71510000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G65" t="n">
-        <v>26.4151</v>
+        <v>14.5251</v>
       </c>
       <c r="H65" t="n">
-        <v>0.04</v>
+        <v>0.51</v>
       </c>
       <c r="I65" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>timer_info_get</t>
+          <t>trace_buffer_full_notify</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2700</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>2860</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>5.87413</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>2558</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>89.4406</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>block_pool_info_get</t>
+          <t>module_object_pointer_get_extended</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>932</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>963</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.34995</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>926</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>96.15779999999999</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>thread_suspend</t>
+          <t>timer_deactivate</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="C68" t="n">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="D68" t="n">
-        <v>109</v>
+        <v>265</v>
       </c>
       <c r="E68" t="n">
-        <v>35.2751</v>
+        <v>73.00279999999999</v>
       </c>
       <c r="F68" t="n">
         <v>26</v>
       </c>
       <c r="G68" t="n">
-        <v>8.414239999999999</v>
+        <v>7.16253</v>
       </c>
       <c r="H68" t="n">
-        <v>0.15</v>
+        <v>1.1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>queue_info_get</t>
+          <t>thread_performance_system_info_get</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>932</v>
+        <v>34</v>
       </c>
       <c r="C69" t="n">
-        <v>963</v>
+        <v>45</v>
       </c>
       <c r="D69" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.34995</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>926</v>
+        <v>33</v>
       </c>
       <c r="G69" t="n">
-        <v>96.15779999999999</v>
+        <v>73.33329999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1.28</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>event_flags_set_notify</t>
+          <t>mutex_get</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="C70" t="n">
-        <v>106</v>
+        <v>274</v>
       </c>
       <c r="D70" t="n">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="E70" t="n">
-        <v>29.2453</v>
+        <v>39.781</v>
       </c>
       <c r="F70" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G70" t="n">
-        <v>26.4151</v>
+        <v>13.8686</v>
       </c>
       <c r="H70" t="n">
-        <v>0.04</v>
+        <v>0.45</v>
       </c>
       <c r="I70" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>trace_disable</t>
+          <t>block_pool_create</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>8.123250000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>41.7367</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>thread_preemption_change</t>
+          <t>thread_performance_info_get</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="C72" t="n">
-        <v>107</v>
+        <v>355</v>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>23.3645</v>
+        <v>0.28169</v>
       </c>
       <c r="F72" t="n">
-        <v>62</v>
+        <v>326</v>
       </c>
       <c r="G72" t="n">
-        <v>57.9439</v>
+        <v>91.831</v>
       </c>
       <c r="H72" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>trace_interrupt_control</t>
+          <t>trace_user_event_insert</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -2696,184 +2696,184 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>45.4545</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>thread_priority_change</t>
+          <t>event_flags_get</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="C74" t="n">
-        <v>119</v>
+        <v>745</v>
       </c>
       <c r="D74" t="n">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="E74" t="n">
-        <v>21.0084</v>
+        <v>17.8523</v>
       </c>
       <c r="F74" t="n">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="G74" t="n">
-        <v>62.1849</v>
+        <v>30.8725</v>
       </c>
       <c r="H74" t="n">
-        <v>0.03</v>
+        <v>0.55</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>timer_activate</t>
+          <t>queue_create</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="C75" t="n">
-        <v>178</v>
+        <v>373</v>
       </c>
       <c r="D75" t="n">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="E75" t="n">
-        <v>68.5393</v>
+        <v>7.7748</v>
       </c>
       <c r="F75" t="n">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="G75" t="n">
-        <v>14.6067</v>
+        <v>43.6997</v>
       </c>
       <c r="H75" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="I75" t="n">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>trace_buffer_full_notify</t>
+          <t>semaphore_delete</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>19.3798</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>20.155</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>module_object_pointer_get_extended</t>
+          <t>timer_delete</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>25.2525</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>26.2626</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>timer_deactivate</t>
+          <t>thread_interrupt_control</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>304</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>395</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>74.6835</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>6.58228</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>thread_performance_system_info_get</t>
+          <t>mutex_performance_system_info_get</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -2882,450 +2882,16 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G79" t="n">
-        <v>73.33329999999999</v>
+        <v>72</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>thread_info_get</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>3284</v>
-      </c>
-      <c r="C80" t="n">
-        <v>3317</v>
-      </c>
-      <c r="D80" t="n">
-        <v>13</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.39192</v>
-      </c>
-      <c r="F80" t="n">
-        <v>3278</v>
-      </c>
-      <c r="G80" t="n">
-        <v>98.8242</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I80" t="n">
-        <v>4.53</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>mutex_get</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>104</v>
-      </c>
-      <c r="C81" t="n">
-        <v>274</v>
-      </c>
-      <c r="D81" t="n">
-        <v>109</v>
-      </c>
-      <c r="E81" t="n">
-        <v>39.781</v>
-      </c>
-      <c r="F81" t="n">
-        <v>38</v>
-      </c>
-      <c r="G81" t="n">
-        <v>13.8686</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>block_pool_create</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>140</v>
-      </c>
-      <c r="C82" t="n">
-        <v>345</v>
-      </c>
-      <c r="D82" t="n">
-        <v>29</v>
-      </c>
-      <c r="E82" t="n">
-        <v>8.405799999999999</v>
-      </c>
-      <c r="F82" t="n">
-        <v>149</v>
-      </c>
-      <c r="G82" t="n">
-        <v>43.1884</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>thread_performance_info_get</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>320</v>
-      </c>
-      <c r="C83" t="n">
-        <v>355</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.28169</v>
-      </c>
-      <c r="F83" t="n">
-        <v>326</v>
-      </c>
-      <c r="G83" t="n">
-        <v>91.831</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>queue_flush</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>596</v>
-      </c>
-      <c r="C84" t="n">
-        <v>1701</v>
-      </c>
-      <c r="D84" t="n">
-        <v>673</v>
-      </c>
-      <c r="E84" t="n">
-        <v>39.565</v>
-      </c>
-      <c r="F84" t="n">
-        <v>26</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1.52851</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>trace_user_event_insert</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>6</v>
-      </c>
-      <c r="C85" t="n">
-        <v>11</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>5</v>
-      </c>
-      <c r="G85" t="n">
-        <v>45.4545</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>event_flags_set</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>5299</v>
-      </c>
-      <c r="C86" t="n">
-        <v>14993</v>
-      </c>
-      <c r="D86" t="n">
-        <v>5866</v>
-      </c>
-      <c r="E86" t="n">
-        <v>39.1249</v>
-      </c>
-      <c r="F86" t="n">
-        <v>146</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0.973788</v>
-      </c>
-      <c r="H86" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>event_flags_get</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>344</v>
-      </c>
-      <c r="C87" t="n">
-        <v>745</v>
-      </c>
-      <c r="D87" t="n">
-        <v>133</v>
-      </c>
-      <c r="E87" t="n">
-        <v>17.8523</v>
-      </c>
-      <c r="F87" t="n">
-        <v>230</v>
-      </c>
-      <c r="G87" t="n">
-        <v>30.8725</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>queue_create</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>141</v>
-      </c>
-      <c r="C88" t="n">
-        <v>373</v>
-      </c>
-      <c r="D88" t="n">
-        <v>29</v>
-      </c>
-      <c r="E88" t="n">
-        <v>7.7748</v>
-      </c>
-      <c r="F88" t="n">
-        <v>163</v>
-      </c>
-      <c r="G88" t="n">
-        <v>43.6997</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>event_flags_performance_system_info_get</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>13</v>
-      </c>
-      <c r="C89" t="n">
-        <v>17</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>12</v>
-      </c>
-      <c r="G89" t="n">
-        <v>70.5882</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>semaphore_delete</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>32</v>
-      </c>
-      <c r="C90" t="n">
-        <v>129</v>
-      </c>
-      <c r="D90" t="n">
-        <v>25</v>
-      </c>
-      <c r="E90" t="n">
-        <v>19.3798</v>
-      </c>
-      <c r="F90" t="n">
-        <v>26</v>
-      </c>
-      <c r="G90" t="n">
-        <v>20.155</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>timer_delete</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>32</v>
-      </c>
-      <c r="C91" t="n">
-        <v>99</v>
-      </c>
-      <c r="D91" t="n">
-        <v>25</v>
-      </c>
-      <c r="E91" t="n">
-        <v>25.2525</v>
-      </c>
-      <c r="F91" t="n">
-        <v>26</v>
-      </c>
-      <c r="G91" t="n">
-        <v>26.2626</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>thread_interrupt_control</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>mutex_performance_system_info_get</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>19</v>
-      </c>
-      <c r="C93" t="n">
-        <v>25</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>18</v>
-      </c>
-      <c r="G93" t="n">
-        <v>72</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3361,7 +2927,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32932</v>
+        <v>12250</v>
       </c>
     </row>
     <row r="3">
@@ -3371,7 +2937,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>357.96</v>
+        <v>157.05</v>
       </c>
     </row>
     <row r="4">
@@ -3381,7 +2947,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -3391,7 +2957,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5299</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="6">
@@ -3411,7 +2977,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>876</v>
+        <v>275.09</v>
       </c>
     </row>
     <row r="8">
@@ -3421,7 +2987,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72329</v>
+        <v>24105</v>
       </c>
     </row>
     <row r="9">
@@ -3431,7 +2997,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>786.1799999999999</v>
+        <v>309.04</v>
       </c>
     </row>
     <row r="10">
@@ -3441,7 +3007,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="11">
@@ -3451,7 +3017,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14993</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="12">
@@ -3471,7 +3037,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2247.26</v>
+        <v>631.4</v>
       </c>
     </row>
     <row r="14">
@@ -3481,7 +3047,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21697</v>
+        <v>5692</v>
       </c>
     </row>
     <row r="15">
@@ -3491,7 +3057,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235.84</v>
+        <v>72.97</v>
       </c>
     </row>
     <row r="16">
@@ -3501,7 +3067,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -3511,7 +3077,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5866</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="18">
@@ -3531,7 +3097,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15.85</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="20">
@@ -3541,7 +3107,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>74.68000000000001</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -3561,7 +3127,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15568</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="23">
@@ -3571,7 +3137,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>169.22</v>
+        <v>108.63</v>
       </c>
     </row>
     <row r="24">
@@ -3591,7 +3157,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3278</v>
+        <v>926</v>
       </c>
     </row>
     <row r="26">
@@ -3611,7 +3177,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>35.18</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="28">
@@ -3621,7 +3187,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>98.81999999999999</v>
+        <v>96.16</v>
       </c>
     </row>
     <row r="29">
@@ -3641,7 +3207,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
@@ -3652,7 +3218,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>69.57%</t>
+          <t>67.95%</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3229,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
